--- a/data/daily/2026-10/2026-10-17.xlsx
+++ b/data/daily/2026-10/2026-10-17.xlsx
@@ -1195,14 +1195,114 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1450,207 +1450,207 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,13 +2596,29 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16294</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>16296</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>고급스러운 선물용 포장 — 기프트박스 포장이 고급스러워 선물용 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>간편한 복합 섭취 형태 — 액상과 정제가 함께 있어 하나씩 챙겨 먹기 편리함</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>공복 섭취 시 속 불편 — 빈속에 먹었을 때 속이 불편한 느낌이 발생함</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>다소 높은 가격대 — 제품의 가격대가 다소 비싸게 형성되어 있음</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
@@ -2643,12 +2659,28 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15627</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>15631</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>편리한 낱개 휴대성 — 하루치씩 소포장되어 출근이나 여행 시 휴대하기 좋음</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>체력 보충 및 활력 증진 — 피곤하고 기력 없을 때 챙겨 먹으면 활력이 생김</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>선물용 높은 만족도 — 선물로 주고받기에 가치 있고 기분 좋은 제품임</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>즉각적 피로 개선 미흡 — 섭취 직후 피로가 바로 풀리는 것은 아님</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -2692,9 +2724,21 @@
       <c r="J4" t="n">
         <v>3413</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>넉넉한 대용량 구성 — 30개입 이상으로 장기간 복용하거나 나누어 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>피로 회복 및 활력 제공 — 섭취 후 피로감이 줄고 활기찬 하루를 시작하게 됨</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>정성스러운 선물 패키지 — 포장이 예쁘고 마음을 전하기 좋은 건강 선물임</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -2737,12 +2781,28 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>6522</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>6523</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>맛있는 젤리 형태 — 과일맛이 나는 젤리 제형이라 거부감 없이 맛있음</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>어린이 안심 안전캡 — 안전캡 용기가 적용되어 아이가 있는 집에서도 안심됨</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>부담 없는 복용 편의 — 씹어 먹는 방식이라 영양소를 쉽고 편하게 챙김</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>하루 섭취량의 제한 — 맛있어서 더 먹고 싶어도 정해진 양만 먹어야 함</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -2786,9 +2846,21 @@
       <c r="J6" t="n">
         <v>824</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>우수한 피로 회복 효과 — 피로 해소 및 환절기 컨디션 관리에 도움 됨</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>간편한 휴대 및 복용 — 휴대성이 좋아 언제 어디서나 챙겨 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>센스 있는 선물용 추천 — 생일이나 기념일에 받고 만족도가 높은 선물임</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2833,9 +2905,21 @@
       <c r="J7" t="n">
         <v>1771</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>신선한 분말 혼합 방식 — 캡을 누르면 분말과 액상이 바로 섞여 신선하게 섭취함</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>확실한 활력 체감 효과 — 섭취 여부에 따라 피로감과 일상 활력의 차이가 큼</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>고급스러운 제품 포장 — 쇼핑백과 품격 있는 패키지로 선물용으로 적합함</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2880,17 +2964,29 @@
       <c r="J8" t="n">
         <v>785</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>성별 맞춤형 영양 구성 — 남성과 여성을 위한 비타민이 구분되어 있음</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>체감되는 피로 개선 — 복용 시 확실하게 힘이 나고 활력이 도는 느낌임</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>호불호 있는 약 맛 — 오렌지 감기약 느낌의 맛이라 맛이 아쉬움</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2898,38 +2994,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
+          <t>온가족 유산균 선물 ALL NEW 락토핏 골드 3통 + 아임비타 이뮨샷 4병 추가증정</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>32,700원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/682864</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261006173014_9a46de80b829480796c23d0cd4a75de9.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261016132819_da2df5cea93d47b1813674e6bfee72d8.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>837</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+        <v>518</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>합리적인 가성비 구매 — 좋은 가격 구성으로 저렴하게 구매할 수 있음</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>편안해지는 속 상태 — 꾸준히 복용 시 장이 건강해지고 속이 편안해짐</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>신속 정확한 배송 — 택배 배송이 빠르고 정확하게 도착함</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -2945,38 +3053,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10056171</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261006173014_9a46de80b829480796c23d0cd4a75de9.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>8754</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+        <v>837</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>위생적인 이중 제형 — 액상과 정제가 나뉘어 있어 위생적이고 챙기기 편함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>피로 감소 및 면역 관리 — 고함량 비타민 성분으로 활력이 돌고 피로가 덜함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>빠른 배송과 꼼꼼한 포장 — 포장 상태가 양호하고 배송이 빠름</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -2984,7 +3104,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2992,39 +3112,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>온가족 유산균 선물 ALL NEW 락토핏 골드 3통 + 아임비타 이뮨샷 4병 추가증정</t>
+          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32,700원</t>
+          <t>23,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/682864</t>
+          <t>https://gift.kakao.com/product/3252731</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261016132819_da2df5cea93d47b1813674e6bfee72d8.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260909091732_b68718856ae342d0b37c3e36916af86b.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>516</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+        <v>962</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>우수한 감기 예방 효과 — 고함량 비타민C 복용으로 감기와 피로 개선에 도움 됨</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>착한 가격 및 넉넉한 양 — 100포 대용량 구성을 합리적인 가격에 구매함</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>강한 신맛과 쓴맛 — 분말 제형 특성상 신맛과 쓴맛이 강하게 느껴짐</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -3039,7 +3171,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+9포+견과류바 증정</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3049,28 +3181,40 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23,900원</t>
+          <t>41,900원</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261016144543_db4a1b51e2064a748811e238969d0330.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261014082110_1396a6238ec2436a8ec1f9ee6f6c2055.jpg</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>923</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+        <v>1737</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>더부룩함 완화 및 소화 — 체기나 더부룩함이 있을 때 속을 편하게 해줌</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>고소하고 우수한 맛 — 다른 제품에 비해 맛이 고소하고 섭취하기 좋음</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>선물하기 좋은 포장 — 상자 포장이 고급스러워 선물용으로 적합함</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -3086,7 +3230,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+9포+견과류바 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3096,28 +3240,40 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41,900원</t>
+          <t>23,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261014082110_1396a6238ec2436a8ec1f9ee6f6c2055.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261016144543_db4a1b51e2064a748811e238969d0330.jpg</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>1736</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+        <v>923</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>속 편한 소화 개선 — 매일 섭취 시 소화가 잘되고 속이 편안해짐</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>풍부한 추가 구성품 — 견과류바와 추가 증정 포 등 알찬 구성으로 제공됨</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>고소하고 질리지 않는 맛 — 고소한 풍미로 질리지 않고 꾸준히 복용 가능함</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -3160,11 +3316,23 @@
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>263</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+        <v>264</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>기분 좋은 맛있는 효소 — 효소 맛이 맛깔스러워 부담 없이 복용함</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>고퀄리티 굿즈 증정 — 포토카드 및 단백질바 사은품 구성이 훌륭함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>깔끔한 포장과 빠른 배송 — 배송이 빠르고 상품 포장이 매우 깔끔함</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -3209,9 +3377,21 @@
       <c r="J15" t="n">
         <v>69</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>촉촉하고 부드러운 식감 — 퍽퍽하지 않고 촉촉해서 맛있게 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>다양한 맛의 식단 관리 — 양념 맛이 다양해 질리지 않고 식단 유지가 가능함</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>간편한 조리 방식 — 전자레인지에 데우기만 하면 바로 먹을 수 있음</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -3227,41 +3407,61 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>크런틴</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>58,200원</t>
+          <t>45,500원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14408269</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261014163835_db2fb775478047e286699c91aca83ed4.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>든든한 포만감 형성 — 한 팩만으로도 포만감이 커서 식사 대용으로 우수함</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>뛰어난 맛과 가성비 — 떡볶이, 카레 등 맛이 훌륭하며 할인 가성비가 좋음</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>배송 오배송 및 문의 미흡 — 구성품 오배송이 발생하고 고객 문의 응대가 느림</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>포장 터짐 및 진공 불량 — 제품 포장이 터지거나 진공 상태가 헐렁한 경우가 있음</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>다소 자극적인 간 — 일부 제품의 경우 간이 다소 세게 느껴짐</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
@@ -3303,17 +3503,29 @@
       <c r="J17" t="n">
         <v>756</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>고급스러운 예쁜 패키지 — 포장 디자인과 플리츠백 구성이 매우 고급스러움</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 맛있는 앰플 — 맛이 좋아 거부감 없이 매일 챙겨 마시기 편함</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>부담스러운 가격대 — 품질은 좋으나 가격이 비싸 할인 시 구매하게 됨</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3321,38 +3533,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>크런틴</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>58,200원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/14408269</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261014163835_db2fb775478047e286699c91aca83ed4.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>66</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>우수한 맛과 크런치 식감 — 텁텁함 없이 달콤하며 토핑이 씹혀 매우 맛있음</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>오래 지속되는 포만감 — 토핑이 많고 든든하여 아침 식사 대용으로 적합함</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>간편한 파우치 제형 — 물만 넣어 흔들어 마신 후 바로 버릴 수 있어 편리함</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -3360,7 +3584,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3368,40 +3592,60 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>45,500원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>155</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>확실한 숙취 해소 효과 — 음주 전후 복용 시 다음 날 속 더부룩함과 두통이 덜함</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>휴대하기 편한 스틱형 — 스틱 제형이라 가방에 넣고 다니며 나누어 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>부담 없는 은은한 단맛 — 벌꿀이 함유되어 있어 자극 없이 맛있게 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>씁쓸한 한약 맛 — 달달하기보다는 씁쓸한 한약 맛이 날 수 있음</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>개인 사용 시 과한 포장 — 선물세트 포장이라 직접 먹는 용도로는 포장이 과함</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="38" customHeight="1">
@@ -3442,12 +3686,28 @@
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>29</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 음료 제형 — 단백질 특유의 비리고 텁텁한 맛이 없음</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>속 편한 락토프리 — 유당 걱정 없이 속 편하게 마실 수 있음</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>빠른 배송 및 사은품 — 배송이 빠르고 프로틴바 사은품이 증정됨</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>일부 맛의 느끼함 — 밀크바나나 등 일부 맛은 약간 느끼하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3491,8 +3751,16 @@
       <c r="J21" t="n">
         <v>218</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>일반 음료 같은 우수한 맛 — 비린 맛 없이 달달한 라떼나 초코우유 맛이 남</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>운동 후 식사 대용 — 운동 후나 입 심심할 때 마시면 은근히 배가 차오름</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -3644,17 +3912,17 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
     </row>
@@ -3701,17 +3969,17 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>종근당건강</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>뉴트리포유</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>고려은단</t>
         </is>
       </c>
     </row>
@@ -3758,17 +4026,17 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>온가족 유산균 선물 ALL NEW 락토핏 골드 3통 + 아임비타 이뮨샷 4병 추가증정</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>온가족 유산균 선물 ALL NEW 락토핏 골드 3통 + 아임비타 이뮨샷 4병 추가증정</t>
+          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
         </is>
       </c>
     </row>
@@ -3816,16 +4084,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16294</v>
+        <v>16296</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15627</v>
+        <v>15631</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3413</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6522</v>
+        <v>6523</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>824</v>
@@ -3837,48 +4105,126 @@
         <v>785</v>
       </c>
       <c r="J7" s="3" t="n">
+        <v>518</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>837</v>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>8754</v>
-      </c>
       <c r="L7" s="3" t="n">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>고급스러운 선물용 포장 — 기프트박스 포장이 고급스러워 선물용 만족도가 높음
+간편한 복합 섭취 형태 — 액상과 정제가 함께 있어 하나씩 챙겨 먹기 편리함</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>편리한 낱개 휴대성 — 하루치씩 소포장되어 출근이나 여행 시 휴대하기 좋음
+체력 보충 및 활력 증진 — 피곤하고 기력 없을 때 챙겨 먹으면 활력이 생김
+선물용 높은 만족도 — 선물로 주고받기에 가치 있고 기분 좋은 제품임</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>넉넉한 대용량 구성 — 30개입 이상으로 장기간 복용하거나 나누어 먹기 좋음
+피로 회복 및 활력 제공 — 섭취 후 피로감이 줄고 활기찬 하루를 시작하게 됨
+정성스러운 선물 패키지 — 포장이 예쁘고 마음을 전하기 좋은 건강 선물임</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 젤리 형태 — 과일맛이 나는 젤리 제형이라 거부감 없이 맛있음
+어린이 안심 안전캡 — 안전캡 용기가 적용되어 아이가 있는 집에서도 안심됨
+부담 없는 복용 편의 — 씹어 먹는 방식이라 영양소를 쉽고 편하게 챙김</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>우수한 피로 회복 효과 — 피로 해소 및 환절기 컨디션 관리에 도움 됨
+간편한 휴대 및 복용 — 휴대성이 좋아 언제 어디서나 챙겨 먹기 편함
+센스 있는 선물용 추천 — 생일이나 기념일에 받고 만족도가 높은 선물임</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>신선한 분말 혼합 방식 — 캡을 누르면 분말과 액상이 바로 섞여 신선하게 섭취함
+확실한 활력 체감 효과 — 섭취 여부에 따라 피로감과 일상 활력의 차이가 큼
+고급스러운 제품 포장 — 쇼핑백과 품격 있는 패키지로 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>성별 맞춤형 영양 구성 — 남성과 여성을 위한 비타민이 구분되어 있음
+체감되는 피로 개선 — 복용 시 확실하게 힘이 나고 활력이 도는 느낌임</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>합리적인 가성비 구매 — 좋은 가격 구성으로 저렴하게 구매할 수 있음
+편안해지는 속 상태 — 꾸준히 복용 시 장이 건강해지고 속이 편안해짐
+신속 정확한 배송 — 택배 배송이 빠르고 정확하게 도착함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>위생적인 이중 제형 — 액상과 정제가 나뉘어 있어 위생적이고 챙기기 편함
+피로 감소 및 면역 관리 — 고함량 비타민 성분으로 활력이 돌고 피로가 덜함
+빠른 배송과 꼼꼼한 포장 — 포장 상태가 양호하고 배송이 빠름</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>우수한 감기 예방 효과 — 고함량 비타민C 복용으로 감기와 피로 개선에 도움 됨
+착한 가격 및 넉넉한 양 — 100포 대용량 구성을 합리적인 가격에 구매함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>공복 섭취 시 속 불편 — 빈속에 먹었을 때 속이 불편한 느낌이 발생함
+다소 높은 가격대 — 제품의 가격대가 다소 비싸게 형성되어 있음</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>즉각적 피로 개선 미흡 — 섭취 직후 피로가 바로 풀리는 것은 아님</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>하루 섭취량의 제한 — 맛있어서 더 먹고 싶어도 정해진 양만 먹어야 함</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>호불호 있는 약 맛 — 오렌지 감기약 느낌의 맛이라 맛이 아쉬움</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>강한 신맛과 쓴맛 — 분말 제형 특성상 신맛과 쓴맛이 강하게 느껴짐</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -3923,17 +4269,17 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>32,700원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>52,900원</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>19,900원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>32,700원</t>
+          <t>23,900원</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4452,12 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -4153,22 +4499,22 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
           <t>크런틴</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>알디콤</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -4190,14 +4536,14 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+9포+견과류바 증정</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+9포+견과류바 증정</t>
-        </is>
-      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
@@ -4210,22 +4556,22 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
           <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -4283,54 +4629,111 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
+        <v>1737</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>923</v>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>1736</v>
-      </c>
       <c r="E19" s="3" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>69</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>756</v>
       </c>
       <c r="I19" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>155</v>
-      </c>
       <c r="K19" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>218</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="90" customHeight="1">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>더부룩함 완화 및 소화 — 체기나 더부룩함이 있을 때 속을 편하게 해줌
+고소하고 우수한 맛 — 다른 제품에 비해 맛이 고소하고 섭취하기 좋음
+선물하기 좋은 포장 — 상자 포장이 고급스러워 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>속 편한 소화 개선 — 매일 섭취 시 소화가 잘되고 속이 편안해짐
+풍부한 추가 구성품 — 견과류바와 추가 증정 포 등 알찬 구성으로 제공됨
+고소하고 질리지 않는 맛 — 고소한 풍미로 질리지 않고 꾸준히 복용 가능함</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>기분 좋은 맛있는 효소 — 효소 맛이 맛깔스러워 부담 없이 복용함
+고퀄리티 굿즈 증정 — 포토카드 및 단백질바 사은품 구성이 훌륭함
+깔끔한 포장과 빠른 배송 — 배송이 빠르고 상품 포장이 매우 깔끔함</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>촉촉하고 부드러운 식감 — 퍽퍽하지 않고 촉촉해서 맛있게 먹기 좋음
+다양한 맛의 식단 관리 — 양념 맛이 다양해 질리지 않고 식단 유지가 가능함
+간편한 조리 방식 — 전자레인지에 데우기만 하면 바로 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>든든한 포만감 형성 — 한 팩만으로도 포만감이 커서 식사 대용으로 우수함
+뛰어난 맛과 가성비 — 떡볶이, 카레 등 맛이 훌륭하며 할인 가성비가 좋음</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>고급스러운 예쁜 패키지 — 포장 디자인과 플리츠백 구성이 매우 고급스러움
+비린 맛 없는 맛있는 앰플 — 맛이 좋아 거부감 없이 매일 챙겨 마시기 편함</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>우수한 맛과 크런치 식감 — 텁텁함 없이 달콤하며 토핑이 씹혀 매우 맛있음
+오래 지속되는 포만감 — 토핑이 많고 든든하여 아침 식사 대용으로 적합함
+간편한 파우치 제형 — 물만 넣어 흔들어 마신 후 바로 버릴 수 있어 편리함</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>확실한 숙취 해소 효과 — 음주 전후 복용 시 다음 날 속 더부룩함과 두통이 덜함
+휴대하기 편한 스틱형 — 스틱 제형이라 가방에 넣고 다니며 나누어 먹기 좋음
+부담 없는 은은한 단맛 — 벌꿀이 함유되어 있어 자극 없이 맛있게 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 음료 제형 — 단백질 특유의 비리고 텁텁한 맛이 없음
+속 편한 락토프리 — 유당 걱정 없이 속 편하게 마실 수 있음
+빠른 배송 및 사은품 — 배송이 빠르고 프로틴바 사은품이 증정됨</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>일반 음료 같은 우수한 맛 — 비린 맛 없이 달달한 라떼나 초코우유 맛이 남
+운동 후 식사 대용 — 운동 후나 입 심심할 때 마시면 은근히 배가 차오름</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4340,11 +4743,30 @@
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>배송 오배송 및 문의 미흡 — 구성품 오배송이 발생하고 고객 문의 응대가 느림
+포장 터짐 및 진공 불량 — 제품 포장이 터지거나 진공 상태가 헐렁한 경우가 있음
+다소 자극적인 간 — 일부 제품의 경우 간이 다소 세게 느껴짐</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>부담스러운 가격대 — 품질은 좋으나 가격이 비싸 할인 시 구매하게 됨</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>씁쓸한 한약 맛 — 달달하기보다는 씁쓸한 한약 맛이 날 수 있음
+개인 사용 시 과한 포장 — 선물세트 포장이라 직접 먹는 용도로는 포장이 과함</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>일부 맛의 느끼함 — 밀크바나나 등 일부 맛은 약간 느끼하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
@@ -4355,14 +4777,14 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>41,900원</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
           <t>23,900원</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>41,900원</t>
-        </is>
-      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
           <t>26,900원</t>
@@ -4375,22 +4797,22 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>45,500원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>65,900원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
           <t>58,200원</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>65,900원</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>33,200원</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>45,500원</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -4590,7 +5012,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4598,37 +5020,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>영진 비타민D 1000IU 아연 츄어블 12정</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>영진약품</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=286314184&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260310/KC1U8zhHXeeJFHKQB2Hr286314184_00_01KC1U8zhHXeeJFHKQB2Hr.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>766</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>533</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>물 없이 먹는 츄어블 — 씹어 먹는 타입이라 물 없이도 맛있게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>뛰어난 천원의 가성비 — 가격이 매우 저렴하여 부담 없이 구매할 수 있음</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -4637,7 +5067,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4645,12 +5075,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
+          <t>대웅제약 활성엽산400 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4660,31 +5090,43 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911092&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000202&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260814/qU3FUPerTqzVYxrqf7Lx610911092_00_01qU3FUPerTqzVYxrqf7Lx.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251121/vNZekx45iLI6pl2rDCzm600000202_00_01vNZekx45iLI6pl2rDCzm.png</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>196</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+        <v>623</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>부담 없는 알뜰 가성비 — 다이소에서 저렴하게 구매할 수 있어 가성비가 좋음</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>불편함 없는 순한 복용 — 복용 시 특별한 부작용이나 이상 반응이 없음</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>큰 알약의 목넘김 불편 — 알약 크기가 커서 삼킬 때 목넘김이 다소 불편함</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4692,12 +5134,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4707,31 +5149,43 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2235</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+        <v>7387</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>단일 성분 영양제 구매 — 필요한 코엔자임Q10만 깔끔하게 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>저렴한 입문용 가격 — 가격이 저렴해 처음 영양제를 시도하기에 좋음</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>미비한 효능 체감 — 눈에 띄는 확실한 효과나 변화는 느껴지지 않음</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4739,7 +5193,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4749,27 +5203,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>7380</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+        <v>6934</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>높은 신뢰도와 가성비 — 제약사 브랜드를 착한 가격에 믿고 구매함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>지속적인 재구매 복용 — 만족도가 높아 꾸준히 챙겨 먹는 제품임</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -4778,7 +5240,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4786,7 +5248,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4796,27 +5258,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000281&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/H44oDYbaAQPekxvnTd9T600000281_00_01H44oDYbaAQPekxvnTd9T.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>355</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+        <v>5253</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>혈당 케어 기대감 — 식후 당스파이크 관리에 도움이 되는 느낌임</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>저렴한 부담 없는 가격 — 가성비가 좋아 부담 없이 챙겨 먹을 수 있음</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -4825,7 +5295,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4833,12 +5303,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4848,31 +5318,43 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J7" t="n">
-        <v>6931</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+        <v>293</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>상쾌한 구강 청량감 — 레몬민트 맛으로 입안과 식도까지 화하고 상쾌해짐</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>가글 대체 유용성 — 가글을 하기 힘든 상황에서 간편하게 입안 케어 가능함</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1일 1개 섭취 제한 — 하루에 한 번만 먹어야 하는 섭취량 제한이 아쉬움</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4880,37 +5362,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>동국제약 비타민D 2000IU 40캡슐 40일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910777&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251229/5qFLremik89lsUa72Yqy610910777_00_005qFLremik89lsUa72Yqy.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1509</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+        <v>1278</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>작고 편한 캡슐 크기 — 알약 사이즈가 작아 삼키기 편함</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>합리적 용량과 가성비 — 40일분 용량 대비 가격이 저렴하여 가볍게 먹기 좋음</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -4927,12 +5417,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4942,22 +5432,30 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000139&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032640075&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/Am2C7Da2wracg1TigkAF600000139_00_00Am2C7Da2wracg1TigkAF.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260312/0RECqyOK2V8qTztn2K7E032640075_00_000RECqyOK2V8qTztn2K7E.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2503</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+        <v>1140</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>간편한 개별 포장 — 1포씩 소포장되어 외출, 여행, 요리 시 활용도가 높음</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>부담을 줄인 가성비 — 비싼 올리브유를 저렴하고 퀄리티 좋게 이용 가능함</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -4974,46 +5472,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260409/2cHZmOZUJJcZL1ip2bls610910968_00_002cHZmOZUJJcZL1ip2bls.png</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>4101</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>2608</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>맛있는 파인애플 맛 — 상큼한 파인애플 맛 캔디라 거부감 없이 맛있음</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>부담 없는 간식용 섭취 — 회사에서 입이 심심하거나 단것이 당길 때 먹기 좋음</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>붓기 완화 체감 미흡 — 붓기가 빠지는 효능이나 신체 변화는 크지 않음</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5021,12 +5531,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5036,20 +5546,36 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581101&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260601/nkEyZw9TcKRMHbTvSy6D591581101_00_00nkEyZw9TcKRMHbTvSy6D.jpg</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>877</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>알찬 성분의 가성비 — 영양 성분이 골고루 들어있으면서 가격이 저렴함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>데일리 및 여행용 적합 — 휴대하기 편해 회사나 여행지에서 데일리로 먹기 좋음</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>효능 체감의 모호함 — 복용 후 뚜렷한 효과를 직관적으로 느끼기는 어려움</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5164,39 +5690,39 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>비타민D</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
@@ -5209,7 +5735,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -5221,52 +5747,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>영진약품</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>안국약품</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
     </row>
@@ -5278,52 +5804,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>영진 비타민D 1000IU 아연 츄어블 12정</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
+          <t>대웅제약 활성엽산400 30정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>동국제약 비타민D 2000IU 40캡슐 40일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5334,10 +5860,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
@@ -5349,18 +5875,20 @@
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -5369,50 +5897,102 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>766</v>
+        <v>533</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>196</v>
+        <v>623</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2235</v>
+        <v>7387</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7380</v>
+        <v>6934</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>355</v>
+        <v>5253</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>6931</v>
+        <v>293</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1509</v>
+        <v>1278</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2503</v>
+        <v>1140</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>4101</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
+        <v>2608</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>물 없이 먹는 츄어블 — 씹어 먹는 타입이라 물 없이도 맛있게 섭취 가능함
+뛰어난 천원의 가성비 — 가격이 매우 저렴하여 부담 없이 구매할 수 있음</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>부담 없는 알뜰 가성비 — 다이소에서 저렴하게 구매할 수 있어 가성비가 좋음
+불편함 없는 순한 복용 — 복용 시 특별한 부작용이나 이상 반응이 없음</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>단일 성분 영양제 구매 — 필요한 코엔자임Q10만 깔끔하게 챙길 수 있음
+저렴한 입문용 가격 — 가격이 저렴해 처음 영양제를 시도하기에 좋음</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>높은 신뢰도와 가성비 — 제약사 브랜드를 착한 가격에 믿고 구매함
+지속적인 재구매 복용 — 만족도가 높아 꾸준히 챙겨 먹는 제품임</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>혈당 케어 기대감 — 식후 당스파이크 관리에 도움이 되는 느낌임
+저렴한 부담 없는 가격 — 가성비가 좋아 부담 없이 챙겨 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>상쾌한 구강 청량감 — 레몬민트 맛으로 입안과 식도까지 화하고 상쾌해짐
+가글 대체 유용성 — 가글을 하기 힘든 상황에서 간편하게 입안 케어 가능함</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>작고 편한 캡슐 크기 — 알약 사이즈가 작아 삼키기 편함
+합리적 용량과 가성비 — 40일분 용량 대비 가격이 저렴하여 가볍게 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>간편한 개별 포장 — 1포씩 소포장되어 외출, 여행, 요리 시 활용도가 높음
+부담을 줄인 가성비 — 비싼 올리브유를 저렴하고 퀄리티 좋게 이용 가능함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 파인애플 맛 — 상큼한 파인애플 맛 캔디라 거부감 없이 맛있음
+부담 없는 간식용 섭취 — 회사에서 입이 심심하거나 단것이 당길 때 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>알찬 성분의 가성비 — 영양 성분이 골고루 들어있으면서 가격이 저렴함
+데일리 및 여행용 적합 — 휴대하기 편해 회사나 여행지에서 데일리로 먹기 좋음</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -5421,15 +6001,35 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>큰 알약의 목넘김 불편 — 알약 크기가 커서 삼킬 때 목넘김이 다소 불편함</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>미비한 효능 체감 — 눈에 띄는 확실한 효과나 변화는 느껴지지 않음</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>1일 1개 섭취 제한 — 하루에 한 번만 먹어야 하는 섭취량 제한이 아쉬움</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>붓기 완화 체감 미흡 — 붓기가 빠지는 효능이나 신체 변화는 크지 않음</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>효능 체감의 모호함 — 복용 후 뚜렷한 효과를 직관적으로 느끼기는 어려움</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -5439,7 +6039,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -5454,32 +6054,32 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5663,7 +6263,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5671,27 +6271,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -5706,7 +6306,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5714,27 +6314,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355482ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -5749,7 +6349,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5757,27 +6357,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>글로우뮤즈</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>26,800원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -5792,7 +6392,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5800,33 +6400,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355482ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>장과 체지방 이중 케어 — 장 건강과 체지방 감소를 한 번에 관리할 수 있음</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>상큼한 요거트 맛 — 맛있는 요거트 맛이라 하루 한 포씩 챙겨 먹기 좋음</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -5835,7 +6443,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5843,31 +6451,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587422ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25525</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -5878,7 +6490,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5886,27 +6498,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 (1개월분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>115,000원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000207974&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020797409ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -5921,7 +6533,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5929,35 +6541,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>8576</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -5968,7 +6576,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5976,31 +6584,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
+          <t>[1+1]알디콤 Plus 숙취해소제 21ml 4포입</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24,000원</t>
+          <t>17,300원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261662&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227457&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026166204ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022745735ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3685</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -6011,7 +6623,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6019,38 +6631,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>21021</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492948ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>매우 작은 캡슐 크기 — 캡슐 크기가 작고 가벼워 목넘김이 극도로 편함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>질과 장 더블 케어 — 질 건강과 장 건강을 한 번에 케어할 수 있음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>매력적인 콜라보 굿즈 — 카드케이스 등 귀여운 굿즈가 포함되어 만족스러움</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -6058,7 +6678,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6066,39 +6686,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>헬스헬퍼</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237482&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023748215ko.png?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>623</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>1595</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>식후 간편한 복용 — 식후 15분 내 챙겨 먹는 다이어트 보조제임</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>목에 붙는 느낌의 불편함 — 알약 삼킬 때 목에 붙는 듯한 이물감이 약간 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -6213,52 +6841,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -6270,52 +6898,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>글로우뮤즈</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>푸드올로지</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>올더베러</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>헬스헬퍼</t>
         </is>
       </c>
     </row>
@@ -6327,52 +6955,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 (1개월분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
+          <t>[1+1]알디콤 Plus 숙취해소제 21ml 4포입</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
         </is>
       </c>
     </row>
@@ -6386,17 +7014,17 @@
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -6409,20 +7037,20 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="n">
+        <v>25525</v>
+      </c>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="n">
-        <v>8576</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="n">
-        <v>21021</v>
-      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>3685</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="n">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -6431,13 +7059,28 @@
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>장과 체지방 이중 케어 — 장 건강과 체지방 감소를 한 번에 관리할 수 있음
+상큼한 요거트 맛 — 맛있는 요거트 맛이라 하루 한 포씩 챙겨 먹기 좋음</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>매우 작은 캡슐 크기 — 캡슐 크기가 작고 가벼워 목넘김이 극도로 편함
+질과 장 더블 케어 — 질 건강과 장 건강을 한 번에 케어할 수 있음
+매력적인 콜라보 굿즈 — 카드케이스 등 귀여운 굿즈가 포함되어 만족스러움</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>식후 간편한 복용 — 식후 15분 내 챙겨 먹는 다이어트 보조제임</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -6454,7 +7097,11 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>목에 붙는 느낌의 불편함 — 알약 삼킬 때 목에 붙는 듯한 이물감이 약간 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6464,52 +7111,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>14,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>26,800원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>30,400원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>17,900원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>14,900원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>10,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>115,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>31,400원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>24,000원</t>
+          <t>17,300원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>18,900원</t>
         </is>
       </c>
     </row>
@@ -6597,7 +7244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6639,25 +7286,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -6667,35 +7314,35 @@
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6745,7 +7392,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6755,10 +7402,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -6767,7 +7414,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6777,10 +7424,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -6789,7 +7436,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6799,10 +7446,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6811,7 +7458,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6833,7 +7480,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6849,28 +7496,6 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
